--- a/data/配置表/09_全局参数.xlsx
+++ b/data/配置表/09_全局参数.xlsx
@@ -1,462 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="全局参数表" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="通用消耗表" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="广告点位表" state="visible" r:id="rId6"/>
+    <sheet name="全局参数表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="通用消耗表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="广告点位表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="142">
-  <si>
-    <t>param_key</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>参数唯一key（程序按此读取）[string]</t>
-  </si>
-  <si>
-    <t>参数值（按type解析）[string]</t>
-  </si>
-  <si>
-    <t>值类型 [enum] int / float / bool / string</t>
-  </si>
-  <si>
-    <t>参数说明：控制啥、取值范围 [string]</t>
-  </si>
-  <si>
-    <t>main_stat_k</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>主属性→伤害系数K，战斗系统3.1；属性平A项的转化系数，MVP=1.0</t>
-  </si>
-  <si>
-    <t>crit_rate_base</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>基础暴击率5%；技巧×0.2%叠加，封顶50%</t>
-  </si>
-  <si>
-    <t>crit_mult_base</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>基础暴击倍率150%；叠加封顶300%</t>
-  </si>
-  <si>
-    <t>eff_min</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>释放效率/岗位效率下限50%</t>
-  </si>
-  <si>
-    <t>eff_max</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>释放效率/岗位效率上限200%</t>
-  </si>
-  <si>
-    <t>pct_mod_min</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>增伤减伤合成系数P的下限40%</t>
-  </si>
-  <si>
-    <t>pct_mod_max</t>
-  </si>
-  <si>
-    <t>增伤减伤合成系数P的上限200%</t>
-  </si>
-  <si>
-    <t>defense_k</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>护甲/魔抗/意志换算曲线常数：减伤率=x/(x+60)，上限60%</t>
-  </si>
-  <si>
-    <t>heal_cap_pct</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>单次治疗硬上限=目标HP上限×30%</t>
-  </si>
-  <si>
-    <t>offline_hours_max</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>离线收益时长上限（小时）</t>
-  </si>
-  <si>
-    <t>offline_efficiency</t>
-  </si>
-  <si>
-    <t>离线收益系数50%</t>
-  </si>
-  <si>
-    <t>ad_daily_limit</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>单日激励视频广告上限次数</t>
-  </si>
-  <si>
-    <t>san_critical_thr</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>SAN档阈值-崩溃档上限</t>
-  </si>
-  <si>
-    <t>san_low_thr</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>SAN档阈值-低落档上限</t>
-  </si>
-  <si>
-    <t>san_high_thr</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>SAN档阈值-高昂档下限</t>
-  </si>
-  <si>
-    <t>raid_fail_rate_res</t>
-  </si>
-  <si>
-    <t>战败时遗失资源比例下限30%</t>
-  </si>
-  <si>
-    <t>raid_fail_rate_res_max</t>
-  </si>
-  <si>
-    <t>战败时遗失资源比例上限50%</t>
-  </si>
-  <si>
-    <t>crit_attr_rate</t>
-  </si>
-  <si>
-    <t>技巧每点提供的暴击率加成+0.2%（战斗系统3.3）</t>
-  </si>
-  <si>
-    <t>crit_attr_rate_cap</t>
-  </si>
-  <si>
-    <t>属性来源暴击率加成上限+20%</t>
-  </si>
-  <si>
-    <t>crit_rate_cap</t>
-  </si>
-  <si>
-    <t>暴击率总上限50%</t>
-  </si>
-  <si>
-    <t>crit_mult_cap</t>
-  </si>
-  <si>
-    <t>暴击倍率总上限300%（基础150%+加成）</t>
-  </si>
-  <si>
-    <t>block_rate_base</t>
-  </si>
-  <si>
-    <t>基础格挡率0%</t>
-  </si>
-  <si>
-    <t>block_rate_cap</t>
-  </si>
-  <si>
-    <t>格挡率上限50%</t>
-  </si>
-  <si>
-    <t>block_min_keep</t>
-  </si>
-  <si>
-    <t>格挡成功后至少保留原伤害的10%</t>
-  </si>
-  <si>
-    <t>atk_speed_mod_min</t>
-  </si>
-  <si>
-    <t>攻速修正下限-50%（装备词缀/技能）</t>
-  </si>
-  <si>
-    <t>atk_speed_mod_max</t>
-  </si>
-  <si>
-    <t>攻速修正上限+50%</t>
-  </si>
-  <si>
-    <t>heal_bonus_cap</t>
-  </si>
-  <si>
-    <t>治疗加成（词缀/技能）上限+50%</t>
-  </si>
-  <si>
-    <t>trait_total_max</t>
-  </si>
-  <si>
-    <t>船员特性总数上限（正面+负面合计，正面最多占满5格）</t>
-  </si>
-  <si>
-    <t>trait_pos_max</t>
-  </si>
-  <si>
-    <t>正面特性单独上限（全正面时可占满5格）</t>
-  </si>
-  <si>
-    <t>pos_boss_gain_chance</t>
-  </si>
-  <si>
-    <t>战胜Boss结算时获得正面特性的概率</t>
-  </si>
-  <si>
-    <t>neg_san_gain_chance</t>
-  </si>
-  <si>
-    <t>章内SAN&lt;30结算时获得负面特性的概率</t>
-  </si>
-  <si>
-    <t>neg_san_gain_chapter_max</t>
-  </si>
-  <si>
-    <t>每章SAN&lt;30获得负面特性的次数上限</t>
-  </si>
-  <si>
-    <t>neg_revive_gain_chance</t>
-  </si>
-  <si>
-    <t>死亡复活时获得负面特性的概率（不限次数）</t>
-  </si>
-  <si>
-    <t>pray_clear_cost_shell</t>
-  </si>
-  <si>
-    <t>祈祷室清除1项负面特性的固定贝壳币消耗（不递增）</t>
-  </si>
-  <si>
-    <t>san_max_base</t>
-  </si>
-  <si>
-    <t>SAN基础上限（精神加成：上限=100+精神×san_spirit_max_bonus）</t>
-  </si>
-  <si>
-    <t>san_init</t>
-  </si>
-  <si>
-    <t>船员初始SAN</t>
-  </si>
-  <si>
-    <t>san_regen_per_min</t>
-  </si>
-  <si>
-    <t>SAN自然恢复量/分钟（食物与淡水充足且无袭击时）</t>
-  </si>
-  <si>
-    <t>san_regen_water_bonus</t>
-  </si>
-  <si>
-    <t>淡水充足时SAN恢复加成+50%</t>
-  </si>
-  <si>
-    <t>san_spirit_max_bonus</t>
-  </si>
-  <si>
-    <t>每点精神提供的SAN上限加成</t>
-  </si>
-  <si>
-    <t>cost_id</t>
-  </si>
-  <si>
-    <t>cost_name</t>
-  </si>
-  <si>
-    <t>items_json</t>
-  </si>
-  <si>
-    <t>消耗唯一id [int]</t>
-  </si>
-  <si>
-    <t>消耗名称 [string]</t>
-  </si>
-  <si>
-    <t>消耗的物品列表JSON：[{"item_id":"xxx","count":N},...] [json]</t>
-  </si>
-  <si>
-    <t>说明 [string]</t>
-  </si>
-  <si>
-    <t>商店刷新·贝壳币</t>
-  </si>
-  <si>
-    <t>[{"item_id":"itm_shell","count":100}]</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>转职任务·仪式蜡烛</t>
-  </si>
-  <si>
-    <t>[{"item_id":"itm_ritual_candle","count":3}]</t>
-  </si>
-  <si>
-    <t>教堂祈祷·恢复SAN</t>
-  </si>
-  <si>
-    <t>[{"item_id":"itm_shell","count":200}]</t>
-  </si>
-  <si>
-    <t>幽光教堂事件选项消耗</t>
-  </si>
-  <si>
-    <t>ad_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>scene</t>
-  </si>
-  <si>
-    <t>daily_limit</t>
-  </si>
-  <si>
-    <t>reward_desc</t>
-  </si>
-  <si>
-    <t>点位唯一key [string]</t>
-  </si>
-  <si>
-    <t>点位中文名 [string]</t>
-  </si>
-  <si>
-    <t>触发场景代码 [string]</t>
-  </si>
-  <si>
-    <t>单日上限次数，-1=不限 [int]</t>
-  </si>
-  <si>
-    <t>广告奖励说明 [string]</t>
-  </si>
-  <si>
-    <t>ad_float_again</t>
-  </si>
-  <si>
-    <t>再捞一次</t>
-  </si>
-  <si>
-    <t>floating_pick</t>
-  </si>
-  <si>
-    <t>立刻刷新下一个漂浮物</t>
-  </si>
-  <si>
-    <t>ad_shop_refresh</t>
-  </si>
-  <si>
-    <t>商人岛刷新</t>
-  </si>
-  <si>
-    <t>shop</t>
-  </si>
-  <si>
-    <t>刷新商品列表</t>
-  </si>
-  <si>
-    <t>ad_offline_double</t>
-  </si>
-  <si>
-    <t>离线收益翻倍</t>
-  </si>
-  <si>
-    <t>offline_settle</t>
-  </si>
-  <si>
-    <t>离线收益×2</t>
-  </si>
-  <si>
-    <t>ad_raid_escape</t>
-  </si>
-  <si>
-    <t>逃跑重置</t>
-  </si>
-  <si>
-    <t>battle_escape</t>
-  </si>
-  <si>
-    <t>本次逃跑不消耗能源</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -475,21 +45,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -814,1435 +443,1553 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="4" width="24" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">param_key</t>
+          <t>param_key</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">desc</t>
+          <t>desc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">参数唯一key（程序按此读取）[string]</t>
+          <t>参数唯一key（程序按此读取）[string]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">参数值（按type解析）[string]</t>
+          <t>参数值（按type解析）[string]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">值类型 [enum] int / float / bool / string</t>
+          <t>值类型 [enum] int / float / bool / string</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">参数说明：控制啥、取值范围 [string]</t>
+          <t>参数说明：控制啥、取值范围 [string]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_stat_k</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1.0</v>
+          <t>main_stat_k</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">主属性→伤害系数K，战斗系统3.1；属性平A项的转化系数，MVP=1.0</t>
+          <t>主属性→伤害系数K，战斗系统3.1；属性平A项的转化系数，MVP=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">crit_rate_base</t>
-        </is>
-      </c>
-      <c r="B4">
+          <t>crit_rate_base</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0.05</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">基础暴击率5%；技巧×0.2%叠加，封顶50%</t>
+          <t>基础暴击率5%；技巧×0.2%叠加，封顶50%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">crit_mult_base</t>
-        </is>
-      </c>
-      <c r="B5">
+          <t>crit_mult_base</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">基础暴击倍率150%；叠加封顶300%</t>
+          <t>基础暴击倍率150%；叠加封顶300%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">eff_min</t>
-        </is>
-      </c>
-      <c r="B6">
+          <t>eff_min</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>0.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">释放效率/岗位效率下限50%</t>
+          <t>释放效率/岗位效率下限50%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">eff_max</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2.0</v>
+          <t>eff_max</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">释放效率/岗位效率上限200%</t>
+          <t>释放效率/岗位效率上限200%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pct_mod_min</t>
-        </is>
-      </c>
-      <c r="B8">
+          <t>pct_mod_min</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>0.4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">增伤减伤合成系数P的下限40%</t>
+          <t>增伤减伤合成系数P的下限40%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pct_mod_max</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2.0</v>
+          <t>pct_mod_max</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">增伤减伤合成系数P的上限200%</t>
+          <t>增伤减伤合成系数P的上限200%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">defense_k</t>
-        </is>
-      </c>
-      <c r="B10">
+          <t>defense_k</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>60</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">护甲/魔抗/意志换算曲线常数：减伤率=x/(x+60)，上限60%</t>
+          <t>护甲/魔抗/意志换算曲线常数：减伤率=x/(x+60)，上限60%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">heal_cap_pct</t>
-        </is>
-      </c>
-      <c r="B11">
+          <t>heal_cap_pct</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>0.3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">单次治疗硬上限=目标HP上限×30%</t>
+          <t>单次治疗硬上限=目标HP上限×30%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">offline_hours_max</t>
-        </is>
-      </c>
-      <c r="B12">
+          <t>offline_hours_max</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">离线收益时长上限（小时）</t>
+          <t>离线收益时长上限（小时）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">offline_efficiency</t>
-        </is>
-      </c>
-      <c r="B13">
+          <t>offline_efficiency</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">离线收益系数50%</t>
+          <t>离线收益系数50%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad_daily_limit</t>
-        </is>
-      </c>
-      <c r="B14">
+          <t>ad_daily_limit</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">单日激励视频广告上限次数</t>
+          <t>单日激励视频广告上限次数</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">san_critical_thr</t>
-        </is>
-      </c>
-      <c r="B15">
+          <t>san_critical_thr</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>30</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN档阈值-崩溃档上限</t>
+          <t>SAN档阈值-崩溃档上限</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">san_low_thr</t>
-        </is>
-      </c>
-      <c r="B16">
+          <t>san_low_thr</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>50</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN档阈值-低落档上限</t>
+          <t>SAN档阈值-低落档上限</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">san_high_thr</t>
-        </is>
-      </c>
-      <c r="B17">
+          <t>san_high_thr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>80</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN档阈值-高昂档下限</t>
+          <t>SAN档阈值-高昂档下限</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">raid_fail_rate_res</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>raid_fail_rate_res</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>0.3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">战败时遗失资源比例下限30%</t>
+          <t>战败时遗失资源比例下限30%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">raid_fail_rate_res_max</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>raid_fail_rate_res_max</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>0.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">战败时遗失资源比例上限50%</t>
+          <t>战败时遗失资源比例上限50%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">crit_attr_rate</t>
-        </is>
-      </c>
-      <c r="B20">
+          <t>crit_attr_rate</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>0.002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">技巧每点提供的暴击率加成+0.2%（战斗系统3.3）</t>
+          <t>技巧每点提供的暴击率加成+0.2%（战斗系统3.3）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">crit_attr_rate_cap</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>crit_attr_rate_cap</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>0.2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">属性来源暴击率加成上限+20%</t>
+          <t>属性来源暴击率加成上限+20%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">crit_rate_cap</t>
-        </is>
-      </c>
-      <c r="B22">
+          <t>crit_rate_cap</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>0.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴击率总上限50%</t>
+          <t>暴击率总上限50%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">crit_mult_cap</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>crit_mult_cap</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴击倍率总上限300%（基础150%+加成）</t>
+          <t>暴击倍率总上限300%（基础150%+加成）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">block_rate_base</t>
-        </is>
-      </c>
-      <c r="B24">
+          <t>block_rate_base</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">基础格挡率0%</t>
+          <t>基础格挡率0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">block_rate_cap</t>
-        </is>
-      </c>
-      <c r="B25">
+          <t>block_rate_cap</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>0.5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">格挡率上限50%</t>
+          <t>格挡率上限50%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">block_min_keep</t>
-        </is>
-      </c>
-      <c r="B26">
+          <t>block_min_keep</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>0.1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">格挡成功后至少保留原伤害的10%</t>
+          <t>格挡成功后至少保留原伤害的10%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">atk_speed_mod_min</t>
-        </is>
-      </c>
-      <c r="B27">
+          <t>atk_speed_mod_min</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>-0.5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻速修正下限-50%（装备词缀/技能）</t>
+          <t>攻速修正下限-50%（装备词缀/技能）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">atk_speed_mod_max</t>
-        </is>
-      </c>
-      <c r="B28">
+          <t>atk_speed_mod_max</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>0.5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻速修正上限+50%</t>
+          <t>攻速修正上限+50%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">heal_bonus_cap</t>
-        </is>
-      </c>
-      <c r="B29">
+          <t>heal_bonus_cap</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>0.5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">治疗加成（词缀/技能）上限+50%</t>
+          <t>治疗加成（词缀/技能）上限+50%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">trait_total_max</t>
-        </is>
-      </c>
-      <c r="B30">
+          <t>trait_total_max</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">船员特性总数上限（正面+负面合计，正面最多占满5格）</t>
+          <t>船员特性总数上限（正面+负面合计，正面最多占满5格）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">trait_pos_max</t>
-        </is>
-      </c>
-      <c r="B31">
+          <t>trait_pos_max</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">正面特性单独上限（全正面时可占满5格）</t>
+          <t>正面特性单独上限（全正面时可占满5格）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">pos_boss_gain_chance</t>
-        </is>
-      </c>
-      <c r="B32">
+          <t>pos_boss_gain_chance</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>0.5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">战胜Boss结算时获得正面特性的概率</t>
+          <t>战胜Boss结算时获得正面特性的概率</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">neg_san_gain_chance</t>
-        </is>
-      </c>
-      <c r="B33">
+          <t>neg_san_gain_chance</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>0.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">章内SAN&lt;30结算时获得负面特性的概率</t>
+          <t>章内SAN&lt;30结算时获得负面特性的概率</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">neg_san_gain_chapter_max</t>
-        </is>
-      </c>
-      <c r="B34">
+          <t>neg_san_gain_chapter_max</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">每章SAN&lt;30获得负面特性的次数上限</t>
+          <t>每章SAN&lt;30获得负面特性的次数上限</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">neg_revive_gain_chance</t>
-        </is>
-      </c>
-      <c r="B35">
+          <t>neg_revive_gain_chance</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡复活时获得负面特性的概率（不限次数）</t>
+          <t>死亡复活时获得负面特性的概率（不限次数）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pray_clear_cost_shell</t>
-        </is>
-      </c>
-      <c r="B36">
+          <t>pray_clear_cost_shell</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>300</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">忏悔室（原祈祷室）直接清除1项负面特性的固定贝壳币消耗（不递增）；与「虚空晶→赎罪券」通道并存</t>
+          <t>忏悔室（原祈祷室）直接清除1项负面特性的固定贝壳币消耗（不递增）；与「虚空晶→赎罪券」通道并存</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">san_max_base</t>
-        </is>
-      </c>
-      <c r="B37">
+          <t>san_max_base</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>100</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN基础上限（精神加成：上限=100+精神×san_spirit_max_bonus）</t>
+          <t>SAN基础上限（精神加成：上限=100+精神×san_spirit_max_bonus）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">san_init</t>
-        </is>
-      </c>
-      <c r="B38">
+          <t>san_init</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
         <v>80</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">船员初始SAN</t>
+          <t>船员初始SAN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">san_regen_per_min</t>
-        </is>
-      </c>
-      <c r="B39">
+          <t>san_regen_per_min</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN自然恢复量/分钟（食物与淡水充足且无袭击时）</t>
+          <t>SAN自然恢复量/分钟（食物与淡水充足且无袭击时）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">san_regen_water_bonus</t>
-        </is>
-      </c>
-      <c r="B40">
+          <t>san_regen_water_bonus</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
         <v>0.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">淡水充足时SAN恢复加成+50%</t>
+          <t>淡水充足时SAN恢复加成+50%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">san_spirit_max_bonus</t>
-        </is>
-      </c>
-      <c r="B41">
+          <t>san_spirit_max_bonus</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">每点精神提供的SAN上限加成</t>
+          <t>每点精神提供的SAN上限加成</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">bld_dmg_ratio_normal</t>
-        </is>
-      </c>
-      <c r="B42">
+          <t>bld_dmg_ratio_normal</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
         <v>0.83</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">普通怪的建筑伤害系数：建筑伤害 = attack × 本值（对齐 v3.1 的 攻·船员12 / 攻·房间10）</t>
+          <t>普通怪的建筑伤害系数：建筑伤害 = attack × 本值（对齐 v3.1 的 攻·船员12 / 攻·房间10）</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">bld_dmg_ratio_elite</t>
-        </is>
-      </c>
-      <c r="B43">
+          <t>bld_dmg_ratio_elite</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
         <v>0.34</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">精英怪的建筑伤害系数（精英主要在打人，砸房只有 1/3）</t>
+          <t>精英怪的建筑伤害系数（精英主要在打人，砸房只有 1/3）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">bld_dmg_ratio_miniboss</t>
-        </is>
-      </c>
-      <c r="B44">
+          <t>bld_dmg_ratio_miniboss</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
         <v>0.34</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">小Boss 的建筑伤害系数（沿用精英档）</t>
+          <t>小Boss 的建筑伤害系数（沿用精英档）</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">bld_dmg_ratio_boss</t>
-        </is>
-      </c>
-      <c r="B45">
+          <t>bld_dmg_ratio_boss</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
         <v>0.5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boss 的建筑伤害系数；Boss 对船体 = 对房间 × 50%（与船体溢出规则一致）</t>
+          <t>Boss 的建筑伤害系数；Boss 对船体 = 对房间 × 50%（与船体溢出规则一致）</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena_layer_atk_base</t>
-        </is>
-      </c>
-      <c r="B46">
+          <t>arena_layer_atk_base</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
         <v>100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">竞技场第 n 层敌人基础攻击锚点：100×1.11^(n−1)×0.85。**锚点数值以《11_竞技场.xlsx》层数锚点表为准**（本参数仅作程序缺省公式，段内插值由 11 表锚点驱动）</t>
+          <t>竞技场第 n 层敌人基础攻击锚点：100×1.11^(n−1)×0.85。**锚点数值以《11_竞技场.xlsx》层数锚点表为准**（本参数仅作程序缺省公式，段内插值由 11 表锚点驱动）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">island_node_count</t>
-        </is>
-      </c>
-      <c r="B47">
+          <t>island_node_count</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
         <v>5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">遗迹岛的探索节点数。原 10 表 island.node_count，7 岛全填 5 —→ 提为全局常数。真要出现 4 或 6 节点的岛，走事件表 node_count 列覆盖（该列默认 0=用本值）</t>
+          <t>遗迹岛的探索节点数。原 10 表 island.node_count，7 岛全填 5 —→ 提为全局常数。真要出现 4 或 6 节点的岛，走事件表 node_count 列覆盖（该列默认 0=用本值）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">island_squad_size</t>
-        </is>
-      </c>
-      <c r="B48">
+          <t>island_squad_size</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">遗迹探索的出战人数。**固定 3 人**，与海面战斗的整队出战区分——探索是"小队渗透"，不是"甲板接舷"</t>
+          <t>遗迹探索的出战人数。**固定 3 人**，与海面战斗的整队出战区分——探索是"小队渗透"，不是"甲板接舷"</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">island_cost_food</t>
-        </is>
-      </c>
-      <c r="B49">
+          <t>island_cost_food</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
         <v>12</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">每次进入遗迹消耗的食物。3 人 × 4 份，与竞技场「人数 × 3」的定价逻辑不同：岛屿是长流程（5 站），所以单价更高</t>
+          <t>每次进入遗迹消耗的食物。3 人 × 4 份，与竞技场「人数 × 3」的定价逻辑不同：岛屿是长流程（5 站），所以单价更高</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">island_rerun_scan_ratio</t>
-        </is>
-      </c>
-      <c r="B50">
+          <t>island_rerun_scan_ratio</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
         <v>0.6</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">重复探索时，已扫过的节点只给 **60%** 的战利品。**首通与复刷必须拉开差距**，否则最优解是刷一座岛</t>
+          <t>重复探索时，已扫过的节点只给 **60%** 的战利品。**首通与复刷必须拉开差距**，否则最优解是刷一座岛</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">island_lose_penalty</t>
-        </is>
-      </c>
-      <c r="B51">
+          <t>island_lose_penalty</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
         <v>0.3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">遗迹判负时普通材料与币的遗失比例。**固定 30%，不掷骰**，与主线战斗的 `raid_fail_rate_res`（30%~50% 随机）区分：探索本来就是自愿深入，罚得确定，玩家才敢做风险决策</t>
+          <t>遗迹判负时普通材料与币的遗失比例。**固定 30%，不掷骰**，与主线战斗的 `raid_fail_rate_res`（30%~50% 随机）区分：探索本来就是自愿深入，罚得确定，玩家才敢做风险决策</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">island_lose_protect</t>
+          <t>island_lose_protect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">装备|图纸|强化石|技能书|橙装碎片</t>
+          <t>装备|图纸|强化石|技能书|橙装碎片</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">判负时**一件不掉**的硬战利品标签（按 | 拆）。判定顺序：先按本表扣除普通材料与币，再把这几个标签的产出原样带回——界面上先报遗失、再报带回，前者是代价，后者是收获</t>
+          <t>判负时**一件不掉**的硬战利品标签（按 | 拆）。判定顺序：先按本表扣除普通材料与币，再把这几个标签的产出原样带回——界面上先报遗失、再报带回，前者是代价，后者是收获</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">life_tick_sec</t>
-        </is>
-      </c>
-      <c r="B53">
+          <t>life_tick_sec</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
         <v>60</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">船员生活结算周期（秒）。每 tick 按在船人头扣生活消耗</t>
-        </is>
-      </c>
-      <c r="D53"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>船员生活结算周期（秒）。每 tick 按在船人头扣生活消耗</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">life_food_per_crew</t>
-        </is>
-      </c>
-      <c r="B54">
+          <t>life_food_per_crew</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">每 tick 每名船员消耗的食物（=每人 2 食/分）</t>
-        </is>
-      </c>
-      <c r="D54"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>每 tick 每名船员消耗的食物（=每人 2 食/分）</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">life_water_per_crew</t>
-        </is>
-      </c>
-      <c r="B55">
+          <t>life_water_per_crew</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">每 tick 每名船员消耗的淡水（=每人 1 水/分）</t>
-        </is>
-      </c>
-      <c r="D55"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>每 tick 每名船员消耗的淡水（=每人 1 水/分）</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">life_starve_food_per_tick</t>
-        </is>
-      </c>
-      <c r="B56">
+          <t>life_starve_food_per_tick</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
         <v>-1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">食物不足时每 tick 全体 SAN 变化</t>
-        </is>
-      </c>
-      <c r="D56"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>食物不足时每 tick 全体 SAN 变化</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">life_thirst_san_per_tick</t>
-        </is>
-      </c>
-      <c r="B57">
+          <t>life_thirst_san_per_tick</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
         <v>-2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">淡水不足时每 tick 全体 SAN 变化（脱水比饥饿狠）</t>
-        </is>
-      </c>
-      <c r="D57"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>淡水不足时每 tick 全体 SAN 变化（脱水比饥饿狠）</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">econ_balance_ratio</t>
-        </is>
-      </c>
-      <c r="B58">
+          <t>econ_balance_ratio</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
         <v>1.1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">达标配置下 总产出:总消耗 的设计锚点（对账用，程序不读）</t>
-        </is>
-      </c>
-      <c r="D58"/>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>达标配置下 总产出:总消耗 的设计锚点（对账用，程序不读）</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">consume_every_sec_key</t>
+          <t>consume_every_sec_key</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">every_sec</t>
+          <t>every_sec</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">consume_json 里"每隔 X 秒扣一次"的字段名（v1.18 新语义，与每周期 every_n_cycles 并存）</t>
-        </is>
-      </c>
-      <c r="D59"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>consume_json 里"每隔 X 秒扣一次"的字段名（v1.18 新语义，与每周期 every_n_cycles 并存）</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">whale_oil_shots</t>
-        </is>
-      </c>
-      <c r="B60">
+          <t>whale_oil_shots</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
         <v>100</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">鲸脂换弹药：1 块鲸脂（sm_whale_oil）可在工坊为 100 发弹药充能（覆盖本航段最先消耗的 100 发）</t>
+          <t>鲸脂换弹药：1 块鲸脂（sm_whale_oil）可在工坊为 100 发弹药充能（覆盖本航段最先消耗的 100 发）</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">whale_oil_dmg_bonus</t>
-        </is>
-      </c>
-      <c r="B61">
+          <t>whale_oil_dmg_bonus</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
         <v>0.1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">鲸脂换弹药：充能期间弹药伤害 +10%（航段级临时 buff，程序状态不建 buff 表；与 5017 工坊产弹并行不冲突）</t>
+          <t>鲸脂换弹药：充能期间弹药伤害 +10%（航段级临时 buff，程序状态不建 buff 表；与 5017 工坊产弹并行不冲突）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">enhance_destroy_stone_refund</t>
-        </is>
-      </c>
-      <c r="B62">
+          <t>enhance_destroy_stone_refund</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
         <v>0.5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">强化损毁时返还的强化石比例（向上取整：+9 损毁返 3 颗 / +10 损毁返 3 颗；《装备与锻造系统》§6.2）</t>
+          <t>强化损毁时返还的强化石比例（向上取整：+9 损毁返 3 颗 / +10 损毁返 3 颗；《装备与锻造系统》§6.2）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="4" width="24" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cost_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cost_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>items_json</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>消耗唯一id [int]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>消耗名称 [string]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>消耗的物品列表JSON：[{"item_id":"xxx","count":N},...] [json]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>说明 [string]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>商店刷新·贝壳币</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[{"item_id":"itm_shell","count":100}]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>转职任务·仪式蜡烛</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[{"item_id":"itm_ritual_candle","count":3}]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>115</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>教堂祈祷·恢复SAN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[{"item_id":"itm_shell","count":200}]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>幽光教堂事件选项消耗</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="5" width="24" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ad_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scene</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>daily_limit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>reward_desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>点位唯一key [string]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>点位中文名 [string]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>触发场景代码 [string]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>单日上限次数，-1=不限 [int]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>广告奖励说明 [string]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ad_float_again</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>再捞一次</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>floating_pick</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>立刻刷新下一个漂浮物</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ad_shop_refresh</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>商人岛刷新</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>刷新商品列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ad_offline_double</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>离线收益翻倍</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>offline_settle</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D6">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>离线收益×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ad_raid_escape</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>逃跑重置</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>battle_escape</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
-        <v>141</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>本次逃跑不消耗能源</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>